--- a/new original/_Lang_Chinese/Lang/CN/Game/Floor.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Floor.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.282</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Floor.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Floor.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="327">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -752,6 +752,24 @@
     <t xml:space="preserve">129</t>
   </si>
   <si>
+    <t xml:space="preserve">130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloud floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雲の床</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alien floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エイリアンの床</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alpha 11.1</t>
   </si>
   <si>
@@ -818,6 +836,12 @@
     <t xml:space="preserve">EA 23.265</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.286</t>
+  </si>
+  <si>
     <t xml:space="preserve">硬土地板</t>
   </si>
   <si>
@@ -966,6 +990,12 @@
   </si>
   <si>
     <t xml:space="preserve">蘑菇地板</t>
+  </si>
+  <si>
+    <t xml:space="preserve">云朵地板</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异形地板</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1101,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1083,10 +1113,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1102,10 +1132,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1121,10 +1151,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1140,10 +1170,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C7" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1159,10 +1189,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C8" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1178,10 +1208,10 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C9" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -1197,10 +1227,10 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C10" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -1216,10 +1246,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C11" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -1235,10 +1265,10 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C12" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
@@ -1254,10 +1284,10 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C13" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
@@ -1273,10 +1303,10 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C14" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D14" t="s">
         <v>37</v>
@@ -1292,10 +1322,10 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C15" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
@@ -1311,10 +1341,10 @@
         <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C16" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D16" t="s">
         <v>41</v>
@@ -1330,10 +1360,10 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C17" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
@@ -1349,10 +1379,10 @@
         <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -1368,10 +1398,10 @@
         <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -1387,10 +1417,10 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C20" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D20" t="s">
         <v>47</v>
@@ -1406,10 +1436,10 @@
         <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C21" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D21" t="s">
         <v>50</v>
@@ -1425,10 +1455,10 @@
         <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C22" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
@@ -1444,10 +1474,10 @@
         <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C23" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -1463,10 +1493,10 @@
         <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C24" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D24" t="s">
         <v>57</v>
@@ -1482,10 +1512,10 @@
         <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C25" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D25" t="s">
         <v>60</v>
@@ -1501,10 +1531,10 @@
         <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C26" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D26" t="s">
         <v>63</v>
@@ -1520,10 +1550,10 @@
         <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C27" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
@@ -1539,10 +1569,10 @@
         <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C28" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D28" t="s">
         <v>29</v>
@@ -1558,10 +1588,10 @@
         <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C29" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D29" t="s">
         <v>29</v>
@@ -1577,10 +1607,10 @@
         <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C30" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D30" t="s">
         <v>69</v>
@@ -1596,10 +1626,10 @@
         <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C31" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
@@ -1615,10 +1645,10 @@
         <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C32" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
@@ -1634,10 +1664,10 @@
         <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C33" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D33" t="s">
         <v>74</v>
@@ -1653,10 +1683,10 @@
         <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C34" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D34" t="s">
         <v>23</v>
@@ -1672,10 +1702,10 @@
         <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C35" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D35" t="s">
         <v>26</v>
@@ -1691,10 +1721,10 @@
         <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C36" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -1710,10 +1740,10 @@
         <v>80</v>
       </c>
       <c r="B37" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C37" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D37" t="s">
         <v>81</v>
@@ -1729,10 +1759,10 @@
         <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C38" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D38" t="s">
         <v>84</v>
@@ -1748,10 +1778,10 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C39" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D39" t="s">
         <v>87</v>
@@ -1767,10 +1797,10 @@
         <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C40" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D40" t="s">
         <v>90</v>
@@ -1786,10 +1816,10 @@
         <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C41" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D41" t="s">
         <v>93</v>
@@ -1805,10 +1835,10 @@
         <v>95</v>
       </c>
       <c r="B42" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C42" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D42" t="s">
         <v>96</v>
@@ -1824,10 +1854,10 @@
         <v>98</v>
       </c>
       <c r="B43" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C43" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D43" t="s">
         <v>99</v>
@@ -1843,10 +1873,10 @@
         <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C44" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="D44" t="s">
         <v>102</v>
@@ -1862,10 +1892,10 @@
         <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C45" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D45" t="s">
         <v>105</v>
@@ -1881,7 +1911,7 @@
         <v>107</v>
       </c>
       <c r="B46" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C46" t="s">
         <v>109</v>
@@ -1900,10 +1930,10 @@
         <v>110</v>
       </c>
       <c r="B47" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C47" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D47" t="s">
         <v>111</v>
@@ -1919,10 +1949,10 @@
         <v>113</v>
       </c>
       <c r="B48" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C48" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D48" t="s">
         <v>102</v>
@@ -1938,10 +1968,10 @@
         <v>115</v>
       </c>
       <c r="B49" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C49" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D49" t="s">
         <v>23</v>
@@ -1957,10 +1987,10 @@
         <v>116</v>
       </c>
       <c r="B50" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C50" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D50" t="s">
         <v>23</v>
@@ -1976,10 +2006,10 @@
         <v>117</v>
       </c>
       <c r="B51" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C51" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D51" t="s">
         <v>69</v>
@@ -1995,10 +2025,10 @@
         <v>118</v>
       </c>
       <c r="B52" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C52" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="D52" t="s">
         <v>119</v>
@@ -2014,10 +2044,10 @@
         <v>121</v>
       </c>
       <c r="B53" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C53" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D53" t="s">
         <v>122</v>
@@ -2033,10 +2063,10 @@
         <v>124</v>
       </c>
       <c r="B54" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C54" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D54" t="s">
         <v>122</v>
@@ -2052,10 +2082,10 @@
         <v>125</v>
       </c>
       <c r="B55" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C55" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D55" t="s">
         <v>26</v>
@@ -2071,10 +2101,10 @@
         <v>126</v>
       </c>
       <c r="B56" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C56" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
@@ -2090,10 +2120,10 @@
         <v>127</v>
       </c>
       <c r="B57" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C57" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="D57" t="s">
         <v>128</v>
@@ -2109,10 +2139,10 @@
         <v>130</v>
       </c>
       <c r="B58" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C58" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D58" t="s">
         <v>23</v>
@@ -2128,10 +2158,10 @@
         <v>131</v>
       </c>
       <c r="B59" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C59" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
@@ -2147,10 +2177,10 @@
         <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C60" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D60" t="s">
         <v>23</v>
@@ -2166,10 +2196,10 @@
         <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C61" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D61" t="s">
         <v>69</v>
@@ -2185,10 +2215,10 @@
         <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C62" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D62" t="s">
         <v>26</v>
@@ -2204,10 +2234,10 @@
         <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C63" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D63" t="s">
         <v>29</v>
@@ -2223,10 +2253,10 @@
         <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C64" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D64" t="s">
         <v>26</v>
@@ -2242,10 +2272,10 @@
         <v>137</v>
       </c>
       <c r="B65" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C65" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D65" t="s">
         <v>29</v>
@@ -2261,10 +2291,10 @@
         <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C66" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D66" t="s">
         <v>29</v>
@@ -2280,10 +2310,10 @@
         <v>139</v>
       </c>
       <c r="B67" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C67" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D67" t="s">
         <v>26</v>
@@ -2299,10 +2329,10 @@
         <v>140</v>
       </c>
       <c r="B68" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C68" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D68" t="s">
         <v>29</v>
@@ -2318,10 +2348,10 @@
         <v>141</v>
       </c>
       <c r="B69" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C69" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D69" t="s">
         <v>63</v>
@@ -2337,10 +2367,10 @@
         <v>142</v>
       </c>
       <c r="B70" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C70" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D70" t="s">
         <v>63</v>
@@ -2356,10 +2386,10 @@
         <v>143</v>
       </c>
       <c r="B71" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C71" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D71" t="s">
         <v>63</v>
@@ -2375,10 +2405,10 @@
         <v>144</v>
       </c>
       <c r="B72" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C72" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D72" t="s">
         <v>63</v>
@@ -2394,10 +2424,10 @@
         <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C73" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D73" t="s">
         <v>63</v>
@@ -2413,10 +2443,10 @@
         <v>146</v>
       </c>
       <c r="B74" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C74" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D74" t="s">
         <v>63</v>
@@ -2432,10 +2462,10 @@
         <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C75" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D75" t="s">
         <v>148</v>
@@ -2451,10 +2481,10 @@
         <v>150</v>
       </c>
       <c r="B76" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C76" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D76" t="s">
         <v>151</v>
@@ -2470,10 +2500,10 @@
         <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C77" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D77" t="s">
         <v>74</v>
@@ -2489,10 +2519,10 @@
         <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C78" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D78" t="s">
         <v>155</v>
@@ -2508,10 +2538,10 @@
         <v>157</v>
       </c>
       <c r="B79" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C79" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D79" t="s">
         <v>158</v>
@@ -2527,10 +2557,10 @@
         <v>160</v>
       </c>
       <c r="B80" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C80" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D80" t="s">
         <v>161</v>
@@ -2546,10 +2576,10 @@
         <v>163</v>
       </c>
       <c r="B81" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C81" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D81" t="s">
         <v>164</v>
@@ -2565,10 +2595,10 @@
         <v>166</v>
       </c>
       <c r="B82" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C82" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D82" t="s">
         <v>164</v>
@@ -2584,10 +2614,10 @@
         <v>167</v>
       </c>
       <c r="B83" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C83" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D83" t="s">
         <v>164</v>
@@ -2603,10 +2633,10 @@
         <v>168</v>
       </c>
       <c r="B84" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C84" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D84" t="s">
         <v>164</v>
@@ -2622,10 +2652,10 @@
         <v>169</v>
       </c>
       <c r="B85" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C85" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D85" t="s">
         <v>170</v>
@@ -2641,10 +2671,10 @@
         <v>172</v>
       </c>
       <c r="B86" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C86" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D86" t="s">
         <v>170</v>
@@ -2660,10 +2690,10 @@
         <v>173</v>
       </c>
       <c r="B87" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C87" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D87" t="s">
         <v>170</v>
@@ -2679,10 +2709,10 @@
         <v>174</v>
       </c>
       <c r="B88" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C88" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D88" t="s">
         <v>170</v>
@@ -2698,10 +2728,10 @@
         <v>175</v>
       </c>
       <c r="B89" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C89" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D89" t="s">
         <v>170</v>
@@ -2717,10 +2747,10 @@
         <v>176</v>
       </c>
       <c r="B90" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C90" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D90" t="s">
         <v>170</v>
@@ -2736,10 +2766,10 @@
         <v>177</v>
       </c>
       <c r="B91" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C91" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D91" t="s">
         <v>170</v>
@@ -2755,10 +2785,10 @@
         <v>178</v>
       </c>
       <c r="B92" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C92" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D92" t="s">
         <v>170</v>
@@ -2774,10 +2804,10 @@
         <v>179</v>
       </c>
       <c r="B93" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C93" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="D93" t="s">
         <v>180</v>
@@ -2793,10 +2823,10 @@
         <v>182</v>
       </c>
       <c r="B94" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C94" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D94" t="s">
         <v>63</v>
@@ -2812,10 +2842,10 @@
         <v>183</v>
       </c>
       <c r="B95" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C95" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D95" t="s">
         <v>164</v>
@@ -2831,10 +2861,10 @@
         <v>184</v>
       </c>
       <c r="B96" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C96" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D96" t="s">
         <v>185</v>
@@ -2850,10 +2880,10 @@
         <v>187</v>
       </c>
       <c r="B97" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C97" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D97" t="s">
         <v>188</v>
@@ -2869,10 +2899,10 @@
         <v>190</v>
       </c>
       <c r="B98" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C98" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D98" t="s">
         <v>188</v>
@@ -2888,10 +2918,10 @@
         <v>191</v>
       </c>
       <c r="B99" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C99" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D99" t="s">
         <v>192</v>
@@ -2907,10 +2937,10 @@
         <v>194</v>
       </c>
       <c r="B100" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C100" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D100" t="s">
         <v>192</v>
@@ -2926,10 +2956,10 @@
         <v>195</v>
       </c>
       <c r="B101" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C101" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D101" t="s">
         <v>185</v>
@@ -2945,10 +2975,10 @@
         <v>196</v>
       </c>
       <c r="B102" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C102" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="D102" t="s">
         <v>197</v>
@@ -2964,10 +2994,10 @@
         <v>199</v>
       </c>
       <c r="B103" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C103" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D103" t="s">
         <v>200</v>
@@ -2983,10 +3013,10 @@
         <v>202</v>
       </c>
       <c r="B104" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C104" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D104" t="s">
         <v>155</v>
@@ -3002,10 +3032,10 @@
         <v>203</v>
       </c>
       <c r="B105" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C105" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D105" t="s">
         <v>69</v>
@@ -3021,10 +3051,10 @@
         <v>204</v>
       </c>
       <c r="B106" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C106" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D106" t="s">
         <v>69</v>
@@ -3040,10 +3070,10 @@
         <v>205</v>
       </c>
       <c r="B107" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C107" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="D107" t="s">
         <v>128</v>
@@ -3059,10 +3089,10 @@
         <v>206</v>
       </c>
       <c r="B108" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C108" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D108" t="s">
         <v>29</v>
@@ -3078,10 +3108,10 @@
         <v>207</v>
       </c>
       <c r="B109" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C109" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D109" t="s">
         <v>26</v>
@@ -3097,10 +3127,10 @@
         <v>208</v>
       </c>
       <c r="B110" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C110" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D110" t="s">
         <v>63</v>
@@ -3116,10 +3146,10 @@
         <v>209</v>
       </c>
       <c r="B111" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D111" t="s">
         <v>26</v>
@@ -3135,10 +3165,10 @@
         <v>210</v>
       </c>
       <c r="B112" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D112" t="s">
         <v>26</v>
@@ -3154,10 +3184,10 @@
         <v>211</v>
       </c>
       <c r="B113" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D113" t="s">
         <v>63</v>
@@ -3173,10 +3203,10 @@
         <v>212</v>
       </c>
       <c r="B114" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D114" t="s">
         <v>63</v>
@@ -3192,10 +3222,10 @@
         <v>213</v>
       </c>
       <c r="B115" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D115" t="s">
         <v>214</v>
@@ -3211,10 +3241,10 @@
         <v>216</v>
       </c>
       <c r="B116" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C116" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D116" t="s">
         <v>217</v>
@@ -3230,10 +3260,10 @@
         <v>219</v>
       </c>
       <c r="B117" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C117" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D117" t="s">
         <v>217</v>
@@ -3249,10 +3279,10 @@
         <v>220</v>
       </c>
       <c r="B118" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C118" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D118" t="s">
         <v>50</v>
@@ -3268,10 +3298,10 @@
         <v>221</v>
       </c>
       <c r="B119" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C119" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D119" t="s">
         <v>50</v>
@@ -3287,10 +3317,10 @@
         <v>222</v>
       </c>
       <c r="B120" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C120" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D120" t="s">
         <v>26</v>
@@ -3306,10 +3336,10 @@
         <v>223</v>
       </c>
       <c r="B121" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C121" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D121" t="s">
         <v>50</v>
@@ -3325,10 +3355,10 @@
         <v>224</v>
       </c>
       <c r="B122" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C122" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D122" t="s">
         <v>50</v>
@@ -3344,10 +3374,10 @@
         <v>225</v>
       </c>
       <c r="B123" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C123" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D123" t="s">
         <v>50</v>
@@ -3363,10 +3393,10 @@
         <v>226</v>
       </c>
       <c r="B124" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C124" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D124" t="s">
         <v>227</v>
@@ -3382,10 +3412,10 @@
         <v>229</v>
       </c>
       <c r="B125" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C125" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="D125" t="s">
         <v>230</v>
@@ -3401,10 +3431,10 @@
         <v>232</v>
       </c>
       <c r="B126" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C126" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="D126" t="s">
         <v>233</v>
@@ -3420,10 +3450,10 @@
         <v>235</v>
       </c>
       <c r="B127" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C127" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D127" t="s">
         <v>236</v>
@@ -3439,10 +3469,10 @@
         <v>238</v>
       </c>
       <c r="B128" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C128" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="D128" t="s">
         <v>239</v>
@@ -3458,10 +3488,10 @@
         <v>241</v>
       </c>
       <c r="B129" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C129" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="D129" t="s">
         <v>239</v>
@@ -3477,10 +3507,10 @@
         <v>242</v>
       </c>
       <c r="B130" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C130" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D130" t="s">
         <v>26</v>
@@ -3496,10 +3526,10 @@
         <v>243</v>
       </c>
       <c r="B131" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C131" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D131" t="s">
         <v>26</v>
@@ -3515,10 +3545,10 @@
         <v>244</v>
       </c>
       <c r="B132" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C132" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D132" t="s">
         <v>26</v>
@@ -3528,6 +3558,44 @@
       </c>
       <c r="G132"/>
       <c r="H132"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>245</v>
+      </c>
+      <c r="B133" t="s">
+        <v>273</v>
+      </c>
+      <c r="C133" t="s">
+        <v>325</v>
+      </c>
+      <c r="D133" t="s">
+        <v>246</v>
+      </c>
+      <c r="E133" t="s">
+        <v>247</v>
+      </c>
+      <c r="G133"/>
+      <c r="H133"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>248</v>
+      </c>
+      <c r="B134" t="s">
+        <v>274</v>
+      </c>
+      <c r="C134" t="s">
+        <v>326</v>
+      </c>
+      <c r="D134" t="s">
+        <v>249</v>
+      </c>
+      <c r="E134" t="s">
+        <v>250</v>
+      </c>
+      <c r="G134"/>
+      <c r="H134"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Floor.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Floor.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="337">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -770,6 +770,27 @@
     <t xml:space="preserve">エイリアンの床</t>
   </si>
   <si>
+    <t xml:space="preserve">132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ステージの床</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alpha 11.1</t>
   </si>
   <si>
@@ -842,6 +863,12 @@
     <t xml:space="preserve">EA 23.286</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.289</t>
+  </si>
+  <si>
     <t xml:space="preserve">硬土地板</t>
   </si>
   <si>
@@ -996,6 +1023,9 @@
   </si>
   <si>
     <t xml:space="preserve">异形地板</t>
+  </si>
+  <si>
+    <t xml:space="preserve">舞台地板</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1131,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1113,10 +1143,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C4" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1132,10 +1162,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C5" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1151,10 +1181,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C6" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1170,10 +1200,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C7" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1189,10 +1219,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C8" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1208,10 +1238,10 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C9" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -1227,10 +1257,10 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C10" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -1246,10 +1276,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C11" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -1265,10 +1295,10 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C12" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
@@ -1284,10 +1314,10 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C13" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
@@ -1303,10 +1333,10 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C14" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D14" t="s">
         <v>37</v>
@@ -1322,10 +1352,10 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C15" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
@@ -1341,10 +1371,10 @@
         <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C16" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="D16" t="s">
         <v>41</v>
@@ -1360,10 +1390,10 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
@@ -1379,10 +1409,10 @@
         <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C18" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -1398,10 +1428,10 @@
         <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C19" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -1417,10 +1447,10 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C20" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D20" t="s">
         <v>47</v>
@@ -1436,10 +1466,10 @@
         <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C21" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D21" t="s">
         <v>50</v>
@@ -1455,10 +1485,10 @@
         <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C22" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
@@ -1474,10 +1504,10 @@
         <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C23" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -1493,10 +1523,10 @@
         <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C24" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D24" t="s">
         <v>57</v>
@@ -1512,10 +1542,10 @@
         <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C25" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D25" t="s">
         <v>60</v>
@@ -1531,10 +1561,10 @@
         <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C26" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D26" t="s">
         <v>63</v>
@@ -1550,10 +1580,10 @@
         <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C27" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
@@ -1569,10 +1599,10 @@
         <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C28" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D28" t="s">
         <v>29</v>
@@ -1588,10 +1618,10 @@
         <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C29" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D29" t="s">
         <v>29</v>
@@ -1607,10 +1637,10 @@
         <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C30" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D30" t="s">
         <v>69</v>
@@ -1626,10 +1656,10 @@
         <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C31" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
@@ -1645,10 +1675,10 @@
         <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C32" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
@@ -1664,10 +1694,10 @@
         <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C33" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D33" t="s">
         <v>74</v>
@@ -1683,10 +1713,10 @@
         <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C34" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D34" t="s">
         <v>23</v>
@@ -1702,10 +1732,10 @@
         <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C35" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D35" t="s">
         <v>26</v>
@@ -1721,10 +1751,10 @@
         <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C36" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -1740,10 +1770,10 @@
         <v>80</v>
       </c>
       <c r="B37" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D37" t="s">
         <v>81</v>
@@ -1759,10 +1789,10 @@
         <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C38" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D38" t="s">
         <v>84</v>
@@ -1778,10 +1808,10 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C39" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D39" t="s">
         <v>87</v>
@@ -1797,10 +1827,10 @@
         <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C40" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D40" t="s">
         <v>90</v>
@@ -1816,10 +1846,10 @@
         <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C41" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D41" t="s">
         <v>93</v>
@@ -1835,10 +1865,10 @@
         <v>95</v>
       </c>
       <c r="B42" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C42" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D42" t="s">
         <v>96</v>
@@ -1854,10 +1884,10 @@
         <v>98</v>
       </c>
       <c r="B43" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C43" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D43" t="s">
         <v>99</v>
@@ -1873,10 +1903,10 @@
         <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C44" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="D44" t="s">
         <v>102</v>
@@ -1892,10 +1922,10 @@
         <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C45" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D45" t="s">
         <v>105</v>
@@ -1911,7 +1941,7 @@
         <v>107</v>
       </c>
       <c r="B46" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C46" t="s">
         <v>109</v>
@@ -1930,10 +1960,10 @@
         <v>110</v>
       </c>
       <c r="B47" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C47" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="D47" t="s">
         <v>111</v>
@@ -1949,10 +1979,10 @@
         <v>113</v>
       </c>
       <c r="B48" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C48" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D48" t="s">
         <v>102</v>
@@ -1968,10 +1998,10 @@
         <v>115</v>
       </c>
       <c r="B49" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C49" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D49" t="s">
         <v>23</v>
@@ -1987,10 +2017,10 @@
         <v>116</v>
       </c>
       <c r="B50" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C50" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D50" t="s">
         <v>23</v>
@@ -2006,10 +2036,10 @@
         <v>117</v>
       </c>
       <c r="B51" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C51" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D51" t="s">
         <v>69</v>
@@ -2025,10 +2055,10 @@
         <v>118</v>
       </c>
       <c r="B52" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C52" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D52" t="s">
         <v>119</v>
@@ -2044,10 +2074,10 @@
         <v>121</v>
       </c>
       <c r="B53" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C53" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D53" t="s">
         <v>122</v>
@@ -2063,10 +2093,10 @@
         <v>124</v>
       </c>
       <c r="B54" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C54" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D54" t="s">
         <v>122</v>
@@ -2082,10 +2112,10 @@
         <v>125</v>
       </c>
       <c r="B55" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C55" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D55" t="s">
         <v>26</v>
@@ -2101,10 +2131,10 @@
         <v>126</v>
       </c>
       <c r="B56" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C56" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
@@ -2120,10 +2150,10 @@
         <v>127</v>
       </c>
       <c r="B57" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C57" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D57" t="s">
         <v>128</v>
@@ -2139,10 +2169,10 @@
         <v>130</v>
       </c>
       <c r="B58" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C58" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D58" t="s">
         <v>23</v>
@@ -2158,10 +2188,10 @@
         <v>131</v>
       </c>
       <c r="B59" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C59" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
@@ -2177,10 +2207,10 @@
         <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C60" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D60" t="s">
         <v>23</v>
@@ -2196,10 +2226,10 @@
         <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C61" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D61" t="s">
         <v>69</v>
@@ -2215,10 +2245,10 @@
         <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C62" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D62" t="s">
         <v>26</v>
@@ -2234,10 +2264,10 @@
         <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C63" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D63" t="s">
         <v>29</v>
@@ -2253,10 +2283,10 @@
         <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C64" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D64" t="s">
         <v>26</v>
@@ -2272,10 +2302,10 @@
         <v>137</v>
       </c>
       <c r="B65" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C65" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D65" t="s">
         <v>29</v>
@@ -2291,10 +2321,10 @@
         <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C66" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D66" t="s">
         <v>29</v>
@@ -2310,10 +2340,10 @@
         <v>139</v>
       </c>
       <c r="B67" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C67" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D67" t="s">
         <v>26</v>
@@ -2329,10 +2359,10 @@
         <v>140</v>
       </c>
       <c r="B68" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C68" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D68" t="s">
         <v>29</v>
@@ -2348,10 +2378,10 @@
         <v>141</v>
       </c>
       <c r="B69" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C69" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D69" t="s">
         <v>63</v>
@@ -2367,10 +2397,10 @@
         <v>142</v>
       </c>
       <c r="B70" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C70" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D70" t="s">
         <v>63</v>
@@ -2386,10 +2416,10 @@
         <v>143</v>
       </c>
       <c r="B71" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C71" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D71" t="s">
         <v>63</v>
@@ -2405,10 +2435,10 @@
         <v>144</v>
       </c>
       <c r="B72" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C72" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D72" t="s">
         <v>63</v>
@@ -2424,10 +2454,10 @@
         <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C73" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D73" t="s">
         <v>63</v>
@@ -2443,10 +2473,10 @@
         <v>146</v>
       </c>
       <c r="B74" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C74" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D74" t="s">
         <v>63</v>
@@ -2462,10 +2492,10 @@
         <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C75" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D75" t="s">
         <v>148</v>
@@ -2481,10 +2511,10 @@
         <v>150</v>
       </c>
       <c r="B76" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C76" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D76" t="s">
         <v>151</v>
@@ -2500,10 +2530,10 @@
         <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C77" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D77" t="s">
         <v>74</v>
@@ -2519,10 +2549,10 @@
         <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C78" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D78" t="s">
         <v>155</v>
@@ -2538,10 +2568,10 @@
         <v>157</v>
       </c>
       <c r="B79" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C79" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D79" t="s">
         <v>158</v>
@@ -2557,10 +2587,10 @@
         <v>160</v>
       </c>
       <c r="B80" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C80" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D80" t="s">
         <v>161</v>
@@ -2576,10 +2606,10 @@
         <v>163</v>
       </c>
       <c r="B81" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C81" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D81" t="s">
         <v>164</v>
@@ -2595,10 +2625,10 @@
         <v>166</v>
       </c>
       <c r="B82" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C82" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D82" t="s">
         <v>164</v>
@@ -2614,10 +2644,10 @@
         <v>167</v>
       </c>
       <c r="B83" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C83" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D83" t="s">
         <v>164</v>
@@ -2633,10 +2663,10 @@
         <v>168</v>
       </c>
       <c r="B84" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C84" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D84" t="s">
         <v>164</v>
@@ -2652,10 +2682,10 @@
         <v>169</v>
       </c>
       <c r="B85" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C85" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D85" t="s">
         <v>170</v>
@@ -2671,10 +2701,10 @@
         <v>172</v>
       </c>
       <c r="B86" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C86" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D86" t="s">
         <v>170</v>
@@ -2690,10 +2720,10 @@
         <v>173</v>
       </c>
       <c r="B87" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C87" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D87" t="s">
         <v>170</v>
@@ -2709,10 +2739,10 @@
         <v>174</v>
       </c>
       <c r="B88" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D88" t="s">
         <v>170</v>
@@ -2728,10 +2758,10 @@
         <v>175</v>
       </c>
       <c r="B89" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C89" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D89" t="s">
         <v>170</v>
@@ -2747,10 +2777,10 @@
         <v>176</v>
       </c>
       <c r="B90" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C90" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D90" t="s">
         <v>170</v>
@@ -2766,10 +2796,10 @@
         <v>177</v>
       </c>
       <c r="B91" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C91" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D91" t="s">
         <v>170</v>
@@ -2785,10 +2815,10 @@
         <v>178</v>
       </c>
       <c r="B92" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C92" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D92" t="s">
         <v>170</v>
@@ -2804,10 +2834,10 @@
         <v>179</v>
       </c>
       <c r="B93" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C93" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D93" t="s">
         <v>180</v>
@@ -2823,10 +2853,10 @@
         <v>182</v>
       </c>
       <c r="B94" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C94" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D94" t="s">
         <v>63</v>
@@ -2842,10 +2872,10 @@
         <v>183</v>
       </c>
       <c r="B95" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D95" t="s">
         <v>164</v>
@@ -2861,10 +2891,10 @@
         <v>184</v>
       </c>
       <c r="B96" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D96" t="s">
         <v>185</v>
@@ -2880,10 +2910,10 @@
         <v>187</v>
       </c>
       <c r="B97" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="D97" t="s">
         <v>188</v>
@@ -2899,10 +2929,10 @@
         <v>190</v>
       </c>
       <c r="B98" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="D98" t="s">
         <v>188</v>
@@ -2918,10 +2948,10 @@
         <v>191</v>
       </c>
       <c r="B99" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D99" t="s">
         <v>192</v>
@@ -2937,10 +2967,10 @@
         <v>194</v>
       </c>
       <c r="B100" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C100" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D100" t="s">
         <v>192</v>
@@ -2956,10 +2986,10 @@
         <v>195</v>
       </c>
       <c r="B101" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C101" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D101" t="s">
         <v>185</v>
@@ -2975,10 +3005,10 @@
         <v>196</v>
       </c>
       <c r="B102" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C102" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D102" t="s">
         <v>197</v>
@@ -2994,10 +3024,10 @@
         <v>199</v>
       </c>
       <c r="B103" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C103" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="D103" t="s">
         <v>200</v>
@@ -3013,10 +3043,10 @@
         <v>202</v>
       </c>
       <c r="B104" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C104" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D104" t="s">
         <v>155</v>
@@ -3032,10 +3062,10 @@
         <v>203</v>
       </c>
       <c r="B105" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C105" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D105" t="s">
         <v>69</v>
@@ -3051,10 +3081,10 @@
         <v>204</v>
       </c>
       <c r="B106" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C106" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D106" t="s">
         <v>69</v>
@@ -3070,10 +3100,10 @@
         <v>205</v>
       </c>
       <c r="B107" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C107" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D107" t="s">
         <v>128</v>
@@ -3089,10 +3119,10 @@
         <v>206</v>
       </c>
       <c r="B108" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C108" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D108" t="s">
         <v>29</v>
@@ -3108,10 +3138,10 @@
         <v>207</v>
       </c>
       <c r="B109" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C109" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D109" t="s">
         <v>26</v>
@@ -3127,10 +3157,10 @@
         <v>208</v>
       </c>
       <c r="B110" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C110" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D110" t="s">
         <v>63</v>
@@ -3146,10 +3176,10 @@
         <v>209</v>
       </c>
       <c r="B111" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C111" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D111" t="s">
         <v>26</v>
@@ -3165,10 +3195,10 @@
         <v>210</v>
       </c>
       <c r="B112" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C112" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D112" t="s">
         <v>26</v>
@@ -3184,10 +3214,10 @@
         <v>211</v>
       </c>
       <c r="B113" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C113" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D113" t="s">
         <v>63</v>
@@ -3203,10 +3233,10 @@
         <v>212</v>
       </c>
       <c r="B114" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C114" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D114" t="s">
         <v>63</v>
@@ -3222,10 +3252,10 @@
         <v>213</v>
       </c>
       <c r="B115" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C115" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D115" t="s">
         <v>214</v>
@@ -3241,10 +3271,10 @@
         <v>216</v>
       </c>
       <c r="B116" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C116" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D116" t="s">
         <v>217</v>
@@ -3260,10 +3290,10 @@
         <v>219</v>
       </c>
       <c r="B117" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C117" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D117" t="s">
         <v>217</v>
@@ -3279,10 +3309,10 @@
         <v>220</v>
       </c>
       <c r="B118" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C118" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D118" t="s">
         <v>50</v>
@@ -3298,10 +3328,10 @@
         <v>221</v>
       </c>
       <c r="B119" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C119" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D119" t="s">
         <v>50</v>
@@ -3317,10 +3347,10 @@
         <v>222</v>
       </c>
       <c r="B120" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C120" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D120" t="s">
         <v>26</v>
@@ -3336,10 +3366,10 @@
         <v>223</v>
       </c>
       <c r="B121" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C121" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D121" t="s">
         <v>50</v>
@@ -3355,10 +3385,10 @@
         <v>224</v>
       </c>
       <c r="B122" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C122" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D122" t="s">
         <v>50</v>
@@ -3374,10 +3404,10 @@
         <v>225</v>
       </c>
       <c r="B123" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C123" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D123" t="s">
         <v>50</v>
@@ -3393,10 +3423,10 @@
         <v>226</v>
       </c>
       <c r="B124" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C124" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="D124" t="s">
         <v>227</v>
@@ -3412,10 +3442,10 @@
         <v>229</v>
       </c>
       <c r="B125" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C125" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="D125" t="s">
         <v>230</v>
@@ -3431,10 +3461,10 @@
         <v>232</v>
       </c>
       <c r="B126" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C126" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="D126" t="s">
         <v>233</v>
@@ -3450,10 +3480,10 @@
         <v>235</v>
       </c>
       <c r="B127" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C127" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D127" t="s">
         <v>236</v>
@@ -3469,10 +3499,10 @@
         <v>238</v>
       </c>
       <c r="B128" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C128" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="D128" t="s">
         <v>239</v>
@@ -3488,10 +3518,10 @@
         <v>241</v>
       </c>
       <c r="B129" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C129" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="D129" t="s">
         <v>239</v>
@@ -3507,10 +3537,10 @@
         <v>242</v>
       </c>
       <c r="B130" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C130" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D130" t="s">
         <v>26</v>
@@ -3526,10 +3556,10 @@
         <v>243</v>
       </c>
       <c r="B131" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C131" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D131" t="s">
         <v>26</v>
@@ -3545,10 +3575,10 @@
         <v>244</v>
       </c>
       <c r="B132" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C132" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D132" t="s">
         <v>26</v>
@@ -3564,10 +3594,10 @@
         <v>245</v>
       </c>
       <c r="B133" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C133" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="D133" t="s">
         <v>246</v>
@@ -3583,10 +3613,10 @@
         <v>248</v>
       </c>
       <c r="B134" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C134" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D134" t="s">
         <v>249</v>
@@ -3596,6 +3626,101 @@
       </c>
       <c r="G134"/>
       <c r="H134"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>251</v>
+      </c>
+      <c r="B135" t="s">
+        <v>282</v>
+      </c>
+      <c r="C135" t="s">
+        <v>336</v>
+      </c>
+      <c r="D135" t="s">
+        <v>252</v>
+      </c>
+      <c r="E135" t="s">
+        <v>253</v>
+      </c>
+      <c r="G135"/>
+      <c r="H135"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>254</v>
+      </c>
+      <c r="B136" t="s">
+        <v>283</v>
+      </c>
+      <c r="C136" t="s">
+        <v>336</v>
+      </c>
+      <c r="D136" t="s">
+        <v>252</v>
+      </c>
+      <c r="E136" t="s">
+        <v>253</v>
+      </c>
+      <c r="G136"/>
+      <c r="H136"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>255</v>
+      </c>
+      <c r="B137" t="s">
+        <v>283</v>
+      </c>
+      <c r="C137" t="s">
+        <v>335</v>
+      </c>
+      <c r="D137" t="s">
+        <v>249</v>
+      </c>
+      <c r="E137" t="s">
+        <v>250</v>
+      </c>
+      <c r="G137"/>
+      <c r="H137"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>256</v>
+      </c>
+      <c r="B138" t="s">
+        <v>283</v>
+      </c>
+      <c r="C138" t="s">
+        <v>335</v>
+      </c>
+      <c r="D138" t="s">
+        <v>249</v>
+      </c>
+      <c r="E138" t="s">
+        <v>250</v>
+      </c>
+      <c r="G138"/>
+      <c r="H138"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>257</v>
+      </c>
+      <c r="B139" t="s">
+        <v>283</v>
+      </c>
+      <c r="C139" t="s">
+        <v>335</v>
+      </c>
+      <c r="D139" t="s">
+        <v>249</v>
+      </c>
+      <c r="E139" t="s">
+        <v>250</v>
+      </c>
+      <c r="G139"/>
+      <c r="H139"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Floor.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Floor.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="327">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -770,27 +770,6 @@
     <t xml:space="preserve">エイリアンの床</t>
   </si>
   <si>
-    <t xml:space="preserve">132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage floor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ステージの床</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alpha 11.1</t>
   </si>
   <si>
@@ -863,12 +842,6 @@
     <t xml:space="preserve">EA 23.286</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.289</t>
-  </si>
-  <si>
     <t xml:space="preserve">硬土地板</t>
   </si>
   <si>
@@ -1023,9 +996,6 @@
   </si>
   <si>
     <t xml:space="preserve">异形地板</t>
-  </si>
-  <si>
-    <t xml:space="preserve">舞台地板</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1101,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1143,10 +1113,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C4" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1162,10 +1132,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1181,10 +1151,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C6" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1200,10 +1170,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C7" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1219,10 +1189,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C8" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1238,10 +1208,10 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C9" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -1257,10 +1227,10 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C10" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -1276,10 +1246,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C11" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -1295,10 +1265,10 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C12" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
@@ -1314,10 +1284,10 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C13" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
@@ -1333,10 +1303,10 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C14" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="D14" t="s">
         <v>37</v>
@@ -1352,10 +1322,10 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C15" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
@@ -1371,10 +1341,10 @@
         <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C16" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="D16" t="s">
         <v>41</v>
@@ -1390,10 +1360,10 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C17" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
@@ -1409,10 +1379,10 @@
         <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -1428,10 +1398,10 @@
         <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -1447,10 +1417,10 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C20" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D20" t="s">
         <v>47</v>
@@ -1466,10 +1436,10 @@
         <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C21" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D21" t="s">
         <v>50</v>
@@ -1485,10 +1455,10 @@
         <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C22" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
@@ -1504,10 +1474,10 @@
         <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C23" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -1523,10 +1493,10 @@
         <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C24" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D24" t="s">
         <v>57</v>
@@ -1542,10 +1512,10 @@
         <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C25" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D25" t="s">
         <v>60</v>
@@ -1561,10 +1531,10 @@
         <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C26" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D26" t="s">
         <v>63</v>
@@ -1580,10 +1550,10 @@
         <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C27" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
@@ -1599,10 +1569,10 @@
         <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C28" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D28" t="s">
         <v>29</v>
@@ -1618,10 +1588,10 @@
         <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C29" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D29" t="s">
         <v>29</v>
@@ -1637,10 +1607,10 @@
         <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C30" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D30" t="s">
         <v>69</v>
@@ -1656,10 +1626,10 @@
         <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C31" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
@@ -1675,10 +1645,10 @@
         <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C32" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
@@ -1694,10 +1664,10 @@
         <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C33" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="D33" t="s">
         <v>74</v>
@@ -1713,10 +1683,10 @@
         <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C34" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D34" t="s">
         <v>23</v>
@@ -1732,10 +1702,10 @@
         <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C35" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D35" t="s">
         <v>26</v>
@@ -1751,10 +1721,10 @@
         <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C36" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -1770,10 +1740,10 @@
         <v>80</v>
       </c>
       <c r="B37" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C37" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D37" t="s">
         <v>81</v>
@@ -1789,10 +1759,10 @@
         <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C38" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="D38" t="s">
         <v>84</v>
@@ -1808,10 +1778,10 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C39" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="D39" t="s">
         <v>87</v>
@@ -1827,10 +1797,10 @@
         <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C40" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D40" t="s">
         <v>90</v>
@@ -1846,10 +1816,10 @@
         <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C41" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D41" t="s">
         <v>93</v>
@@ -1865,10 +1835,10 @@
         <v>95</v>
       </c>
       <c r="B42" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C42" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="D42" t="s">
         <v>96</v>
@@ -1884,10 +1854,10 @@
         <v>98</v>
       </c>
       <c r="B43" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C43" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D43" t="s">
         <v>99</v>
@@ -1903,10 +1873,10 @@
         <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C44" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="D44" t="s">
         <v>102</v>
@@ -1922,10 +1892,10 @@
         <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C45" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D45" t="s">
         <v>105</v>
@@ -1941,7 +1911,7 @@
         <v>107</v>
       </c>
       <c r="B46" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C46" t="s">
         <v>109</v>
@@ -1960,10 +1930,10 @@
         <v>110</v>
       </c>
       <c r="B47" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C47" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D47" t="s">
         <v>111</v>
@@ -1979,10 +1949,10 @@
         <v>113</v>
       </c>
       <c r="B48" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C48" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="D48" t="s">
         <v>102</v>
@@ -1998,10 +1968,10 @@
         <v>115</v>
       </c>
       <c r="B49" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C49" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D49" t="s">
         <v>23</v>
@@ -2017,10 +1987,10 @@
         <v>116</v>
       </c>
       <c r="B50" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C50" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D50" t="s">
         <v>23</v>
@@ -2036,10 +2006,10 @@
         <v>117</v>
       </c>
       <c r="B51" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C51" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D51" t="s">
         <v>69</v>
@@ -2055,10 +2025,10 @@
         <v>118</v>
       </c>
       <c r="B52" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C52" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D52" t="s">
         <v>119</v>
@@ -2074,10 +2044,10 @@
         <v>121</v>
       </c>
       <c r="B53" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C53" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D53" t="s">
         <v>122</v>
@@ -2093,10 +2063,10 @@
         <v>124</v>
       </c>
       <c r="B54" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C54" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D54" t="s">
         <v>122</v>
@@ -2112,10 +2082,10 @@
         <v>125</v>
       </c>
       <c r="B55" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C55" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D55" t="s">
         <v>26</v>
@@ -2131,10 +2101,10 @@
         <v>126</v>
       </c>
       <c r="B56" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C56" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
@@ -2150,10 +2120,10 @@
         <v>127</v>
       </c>
       <c r="B57" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C57" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D57" t="s">
         <v>128</v>
@@ -2169,10 +2139,10 @@
         <v>130</v>
       </c>
       <c r="B58" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C58" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D58" t="s">
         <v>23</v>
@@ -2188,10 +2158,10 @@
         <v>131</v>
       </c>
       <c r="B59" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C59" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
@@ -2207,10 +2177,10 @@
         <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C60" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D60" t="s">
         <v>23</v>
@@ -2226,10 +2196,10 @@
         <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C61" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D61" t="s">
         <v>69</v>
@@ -2245,10 +2215,10 @@
         <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C62" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D62" t="s">
         <v>26</v>
@@ -2264,10 +2234,10 @@
         <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C63" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D63" t="s">
         <v>29</v>
@@ -2283,10 +2253,10 @@
         <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C64" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D64" t="s">
         <v>26</v>
@@ -2302,10 +2272,10 @@
         <v>137</v>
       </c>
       <c r="B65" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C65" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D65" t="s">
         <v>29</v>
@@ -2321,10 +2291,10 @@
         <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C66" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D66" t="s">
         <v>29</v>
@@ -2340,10 +2310,10 @@
         <v>139</v>
       </c>
       <c r="B67" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C67" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D67" t="s">
         <v>26</v>
@@ -2359,10 +2329,10 @@
         <v>140</v>
       </c>
       <c r="B68" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C68" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D68" t="s">
         <v>29</v>
@@ -2378,10 +2348,10 @@
         <v>141</v>
       </c>
       <c r="B69" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C69" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D69" t="s">
         <v>63</v>
@@ -2397,10 +2367,10 @@
         <v>142</v>
       </c>
       <c r="B70" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C70" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D70" t="s">
         <v>63</v>
@@ -2416,10 +2386,10 @@
         <v>143</v>
       </c>
       <c r="B71" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C71" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D71" t="s">
         <v>63</v>
@@ -2435,10 +2405,10 @@
         <v>144</v>
       </c>
       <c r="B72" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C72" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D72" t="s">
         <v>63</v>
@@ -2454,10 +2424,10 @@
         <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C73" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D73" t="s">
         <v>63</v>
@@ -2473,10 +2443,10 @@
         <v>146</v>
       </c>
       <c r="B74" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C74" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D74" t="s">
         <v>63</v>
@@ -2492,10 +2462,10 @@
         <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C75" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="D75" t="s">
         <v>148</v>
@@ -2511,10 +2481,10 @@
         <v>150</v>
       </c>
       <c r="B76" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C76" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D76" t="s">
         <v>151</v>
@@ -2530,10 +2500,10 @@
         <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C77" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="D77" t="s">
         <v>74</v>
@@ -2549,10 +2519,10 @@
         <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C78" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D78" t="s">
         <v>155</v>
@@ -2568,10 +2538,10 @@
         <v>157</v>
       </c>
       <c r="B79" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C79" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D79" t="s">
         <v>158</v>
@@ -2587,10 +2557,10 @@
         <v>160</v>
       </c>
       <c r="B80" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C80" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="D80" t="s">
         <v>161</v>
@@ -2606,10 +2576,10 @@
         <v>163</v>
       </c>
       <c r="B81" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C81" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D81" t="s">
         <v>164</v>
@@ -2625,10 +2595,10 @@
         <v>166</v>
       </c>
       <c r="B82" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C82" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D82" t="s">
         <v>164</v>
@@ -2644,10 +2614,10 @@
         <v>167</v>
       </c>
       <c r="B83" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C83" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D83" t="s">
         <v>164</v>
@@ -2663,10 +2633,10 @@
         <v>168</v>
       </c>
       <c r="B84" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C84" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D84" t="s">
         <v>164</v>
@@ -2682,10 +2652,10 @@
         <v>169</v>
       </c>
       <c r="B85" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C85" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D85" t="s">
         <v>170</v>
@@ -2701,10 +2671,10 @@
         <v>172</v>
       </c>
       <c r="B86" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C86" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D86" t="s">
         <v>170</v>
@@ -2720,10 +2690,10 @@
         <v>173</v>
       </c>
       <c r="B87" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C87" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D87" t="s">
         <v>170</v>
@@ -2739,10 +2709,10 @@
         <v>174</v>
       </c>
       <c r="B88" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C88" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D88" t="s">
         <v>170</v>
@@ -2758,10 +2728,10 @@
         <v>175</v>
       </c>
       <c r="B89" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C89" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D89" t="s">
         <v>170</v>
@@ -2777,10 +2747,10 @@
         <v>176</v>
       </c>
       <c r="B90" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C90" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D90" t="s">
         <v>170</v>
@@ -2796,10 +2766,10 @@
         <v>177</v>
       </c>
       <c r="B91" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C91" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D91" t="s">
         <v>170</v>
@@ -2815,10 +2785,10 @@
         <v>178</v>
       </c>
       <c r="B92" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C92" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D92" t="s">
         <v>170</v>
@@ -2834,10 +2804,10 @@
         <v>179</v>
       </c>
       <c r="B93" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C93" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="D93" t="s">
         <v>180</v>
@@ -2853,10 +2823,10 @@
         <v>182</v>
       </c>
       <c r="B94" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C94" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D94" t="s">
         <v>63</v>
@@ -2872,10 +2842,10 @@
         <v>183</v>
       </c>
       <c r="B95" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C95" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D95" t="s">
         <v>164</v>
@@ -2891,10 +2861,10 @@
         <v>184</v>
       </c>
       <c r="B96" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C96" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D96" t="s">
         <v>185</v>
@@ -2910,10 +2880,10 @@
         <v>187</v>
       </c>
       <c r="B97" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C97" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D97" t="s">
         <v>188</v>
@@ -2929,10 +2899,10 @@
         <v>190</v>
       </c>
       <c r="B98" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C98" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D98" t="s">
         <v>188</v>
@@ -2948,10 +2918,10 @@
         <v>191</v>
       </c>
       <c r="B99" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C99" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D99" t="s">
         <v>192</v>
@@ -2967,10 +2937,10 @@
         <v>194</v>
       </c>
       <c r="B100" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C100" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D100" t="s">
         <v>192</v>
@@ -2986,10 +2956,10 @@
         <v>195</v>
       </c>
       <c r="B101" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C101" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D101" t="s">
         <v>185</v>
@@ -3005,10 +2975,10 @@
         <v>196</v>
       </c>
       <c r="B102" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C102" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D102" t="s">
         <v>197</v>
@@ -3024,10 +2994,10 @@
         <v>199</v>
       </c>
       <c r="B103" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C103" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D103" t="s">
         <v>200</v>
@@ -3043,10 +3013,10 @@
         <v>202</v>
       </c>
       <c r="B104" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C104" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D104" t="s">
         <v>155</v>
@@ -3062,10 +3032,10 @@
         <v>203</v>
       </c>
       <c r="B105" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C105" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D105" t="s">
         <v>69</v>
@@ -3081,10 +3051,10 @@
         <v>204</v>
       </c>
       <c r="B106" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C106" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D106" t="s">
         <v>69</v>
@@ -3100,10 +3070,10 @@
         <v>205</v>
       </c>
       <c r="B107" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C107" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D107" t="s">
         <v>128</v>
@@ -3119,10 +3089,10 @@
         <v>206</v>
       </c>
       <c r="B108" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C108" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D108" t="s">
         <v>29</v>
@@ -3138,10 +3108,10 @@
         <v>207</v>
       </c>
       <c r="B109" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C109" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D109" t="s">
         <v>26</v>
@@ -3157,10 +3127,10 @@
         <v>208</v>
       </c>
       <c r="B110" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C110" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D110" t="s">
         <v>63</v>
@@ -3176,10 +3146,10 @@
         <v>209</v>
       </c>
       <c r="B111" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D111" t="s">
         <v>26</v>
@@ -3195,10 +3165,10 @@
         <v>210</v>
       </c>
       <c r="B112" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D112" t="s">
         <v>26</v>
@@ -3214,10 +3184,10 @@
         <v>211</v>
       </c>
       <c r="B113" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D113" t="s">
         <v>63</v>
@@ -3233,10 +3203,10 @@
         <v>212</v>
       </c>
       <c r="B114" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D114" t="s">
         <v>63</v>
@@ -3252,10 +3222,10 @@
         <v>213</v>
       </c>
       <c r="B115" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D115" t="s">
         <v>214</v>
@@ -3271,10 +3241,10 @@
         <v>216</v>
       </c>
       <c r="B116" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C116" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="D116" t="s">
         <v>217</v>
@@ -3290,10 +3260,10 @@
         <v>219</v>
       </c>
       <c r="B117" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C117" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="D117" t="s">
         <v>217</v>
@@ -3309,10 +3279,10 @@
         <v>220</v>
       </c>
       <c r="B118" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C118" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D118" t="s">
         <v>50</v>
@@ -3328,10 +3298,10 @@
         <v>221</v>
       </c>
       <c r="B119" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C119" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D119" t="s">
         <v>50</v>
@@ -3347,10 +3317,10 @@
         <v>222</v>
       </c>
       <c r="B120" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C120" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D120" t="s">
         <v>26</v>
@@ -3366,10 +3336,10 @@
         <v>223</v>
       </c>
       <c r="B121" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C121" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D121" t="s">
         <v>50</v>
@@ -3385,10 +3355,10 @@
         <v>224</v>
       </c>
       <c r="B122" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C122" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D122" t="s">
         <v>50</v>
@@ -3404,10 +3374,10 @@
         <v>225</v>
       </c>
       <c r="B123" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C123" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D123" t="s">
         <v>50</v>
@@ -3423,10 +3393,10 @@
         <v>226</v>
       </c>
       <c r="B124" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C124" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D124" t="s">
         <v>227</v>
@@ -3442,10 +3412,10 @@
         <v>229</v>
       </c>
       <c r="B125" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C125" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D125" t="s">
         <v>230</v>
@@ -3461,10 +3431,10 @@
         <v>232</v>
       </c>
       <c r="B126" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C126" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D126" t="s">
         <v>233</v>
@@ -3480,10 +3450,10 @@
         <v>235</v>
       </c>
       <c r="B127" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C127" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D127" t="s">
         <v>236</v>
@@ -3499,10 +3469,10 @@
         <v>238</v>
       </c>
       <c r="B128" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C128" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="D128" t="s">
         <v>239</v>
@@ -3518,10 +3488,10 @@
         <v>241</v>
       </c>
       <c r="B129" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C129" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="D129" t="s">
         <v>239</v>
@@ -3537,10 +3507,10 @@
         <v>242</v>
       </c>
       <c r="B130" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C130" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D130" t="s">
         <v>26</v>
@@ -3556,10 +3526,10 @@
         <v>243</v>
       </c>
       <c r="B131" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C131" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D131" t="s">
         <v>26</v>
@@ -3575,10 +3545,10 @@
         <v>244</v>
       </c>
       <c r="B132" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C132" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D132" t="s">
         <v>26</v>
@@ -3594,10 +3564,10 @@
         <v>245</v>
       </c>
       <c r="B133" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C133" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="D133" t="s">
         <v>246</v>
@@ -3613,10 +3583,10 @@
         <v>248</v>
       </c>
       <c r="B134" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C134" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="D134" t="s">
         <v>249</v>
@@ -3626,101 +3596,6 @@
       </c>
       <c r="G134"/>
       <c r="H134"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>251</v>
-      </c>
-      <c r="B135" t="s">
-        <v>282</v>
-      </c>
-      <c r="C135" t="s">
-        <v>336</v>
-      </c>
-      <c r="D135" t="s">
-        <v>252</v>
-      </c>
-      <c r="E135" t="s">
-        <v>253</v>
-      </c>
-      <c r="G135"/>
-      <c r="H135"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>254</v>
-      </c>
-      <c r="B136" t="s">
-        <v>283</v>
-      </c>
-      <c r="C136" t="s">
-        <v>336</v>
-      </c>
-      <c r="D136" t="s">
-        <v>252</v>
-      </c>
-      <c r="E136" t="s">
-        <v>253</v>
-      </c>
-      <c r="G136"/>
-      <c r="H136"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>255</v>
-      </c>
-      <c r="B137" t="s">
-        <v>283</v>
-      </c>
-      <c r="C137" t="s">
-        <v>335</v>
-      </c>
-      <c r="D137" t="s">
-        <v>249</v>
-      </c>
-      <c r="E137" t="s">
-        <v>250</v>
-      </c>
-      <c r="G137"/>
-      <c r="H137"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>256</v>
-      </c>
-      <c r="B138" t="s">
-        <v>283</v>
-      </c>
-      <c r="C138" t="s">
-        <v>335</v>
-      </c>
-      <c r="D138" t="s">
-        <v>249</v>
-      </c>
-      <c r="E138" t="s">
-        <v>250</v>
-      </c>
-      <c r="G138"/>
-      <c r="H138"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>257</v>
-      </c>
-      <c r="B139" t="s">
-        <v>283</v>
-      </c>
-      <c r="C139" t="s">
-        <v>335</v>
-      </c>
-      <c r="D139" t="s">
-        <v>249</v>
-      </c>
-      <c r="E139" t="s">
-        <v>250</v>
-      </c>
-      <c r="G139"/>
-      <c r="H139"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
